--- a/DQ_element_assessment/DQD_Theme_Element_Matrix.xlsx
+++ b/DQ_element_assessment/DQD_Theme_Element_Matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="52">
   <si>
     <t>DQ Dimension</t>
   </si>
@@ -52,40 +52,40 @@
     <t>Completeness</t>
   </si>
   <si>
-    <t>Element missingness</t>
+    <t>Element-level missingness</t>
   </si>
   <si>
     <t>X</t>
   </si>
   <si>
-    <t>Kamdje-Wabo et al., 2019; Khoo &amp; Hasan, 2018; Huang et al., 2021; Barberio et al., 2024; Winkler et al., 2023</t>
+    <t>[48] Barberio; [58] Kamdje-Wabo; [61] Winkler; [62] Khoo and Hasan; [63] Huang</t>
   </si>
   <si>
     <t>Referential completeness</t>
   </si>
   <si>
-    <t>Ammann et al., 2018; Samples et al., 2025; Miller et al., 2015; Barberio et al., 2024; Chughtai et al., 2025; Lloyd et al., 2025; Wang et al., 2025</t>
+    <t>[49] Lloyd; [50] Samples; [51] Chughtai; [52] Wang; [53] Ammann; [54] Miller</t>
   </si>
   <si>
     <t>Temporal completeness</t>
   </si>
   <si>
-    <t>Ditscheid et al., 2020</t>
+    <t>[59] Ditscheid</t>
   </si>
   <si>
     <t>Conformance</t>
   </si>
   <si>
-    <t>Structural nonconformance</t>
-  </si>
-  <si>
-    <t>Kamdje-Wabo et al., 2019; Huang et al., 2021; Ammann et al., 2018; Samples et al., 2025; Barberio et al., 2024; Gadde et al., 2020; Winkler et al., 2023</t>
+    <t>Structural non-conformance</t>
+  </si>
+  <si>
+    <t>[48] Barberio; [49] Lloyd; [50] Samples; [52] Wang; [53] Ammann; [55] Gadde; [58] Kamdje-Wabo; [61] Winkler; [63] Huang</t>
   </si>
   <si>
     <t>Relational conformance</t>
   </si>
   <si>
-    <t>Wang et al., 2025</t>
+    <t>[52] Wang</t>
   </si>
   <si>
     <t>Plausibility</t>
@@ -94,7 +94,7 @@
     <t>Atemporal / temporal plausibility</t>
   </si>
   <si>
-    <t>Kamdje-Wabo et al., 2019; Roos et al., 1982; Huang et al., 2020; Barberio et al., 2024; Gadde et al., 2020; Ditscheid et al., 2020; Hartmann et al., 2016; Winkler et al., 2023</t>
+    <t>[46] Roos; [48] Barberio; [55] Gadde; [58] Kamdje-Wabo; [59] Ditscheid; [60] Hartmann; [61] Winkler; [63] Huang</t>
   </si>
   <si>
     <t>Consistency</t>
@@ -103,28 +103,28 @@
     <t>Temporal inconsistency</t>
   </si>
   <si>
-    <t>Barberio et al., 2024; Ditscheid et al., 2020; Wang et al., 2025</t>
+    <t>[52] Wang; [59] Ditscheid</t>
   </si>
   <si>
     <t>Cross-site inconsistency</t>
   </si>
   <si>
-    <t>Ceratti et al., 2008; Barberio et al., 2024</t>
+    <t>[47] Ceratti; [48] Barberio</t>
   </si>
   <si>
     <t>Relational integrity</t>
   </si>
   <si>
-    <t>Huang et al., 2021; Ammann et al., 2018</t>
-  </si>
-  <si>
-    <t>Accuracy / Correctness</t>
+    <t>[63] Huang; [53] Ammann</t>
+  </si>
+  <si>
+    <t>Accuracy / Correctness / Validity</t>
   </si>
   <si>
     <t>Over / under-detection</t>
   </si>
   <si>
-    <t>Ammann et al., 2018; Maciejewski et al., 2022; Miller et al., 2015; Barberio et al., 2024; Khan et al., 2018</t>
+    <t>[53] Ammann; [64] Maciejewski; [54] Miller; [48] Barberio; [56] Khan</t>
   </si>
   <si>
     <t>Concordance</t>
@@ -133,7 +133,7 @@
     <t>Cross-source disagreement</t>
   </si>
   <si>
-    <t>Ceratti et al., 2008; Chughtai et al., 2025; Laws et al., 2018</t>
+    <t xml:space="preserve">[47] Ceratti; [51] Chughtai; [57] Laws; </t>
   </si>
   <si>
     <t>Uniqueness</t>
@@ -142,7 +142,7 @@
     <t>Duplicate records</t>
   </si>
   <si>
-    <t>Ceratti et al., 2008</t>
+    <t>[47] Ceratti</t>
   </si>
   <si>
     <t>Currency</t>
@@ -151,16 +151,13 @@
     <t>Temporal lag</t>
   </si>
   <si>
-    <t>Ammann et al., 2018; Ditscheid et al., 2020</t>
-  </si>
-  <si>
-    <t>Relevance/Validity</t>
-  </si>
-  <si>
-    <t>Relevance / validity</t>
-  </si>
-  <si>
-    <t>Barberio et al., 2024</t>
+    <t xml:space="preserve">[53] Ammann; [59] Ditscheid </t>
+  </si>
+  <si>
+    <t>Relevance / Fit-for-purpose</t>
+  </si>
+  <si>
+    <t>[48] Barberio</t>
   </si>
   <si>
     <t>Temporal Relationships</t>
@@ -169,7 +166,7 @@
     <t>Date-sequencing</t>
   </si>
   <si>
-    <t>Gadde et al., 2020</t>
+    <t>[55] Gadde</t>
   </si>
   <si>
     <t>Total studies per element</t>
@@ -608,7 +605,7 @@
     <col min="6" max="6" style="12" width="13.005" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="12" width="13.005" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="12" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="10" width="11.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="13" width="11.005" customWidth="1" bestFit="1"/>
     <col min="10" max="10" style="13" width="10.005" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="10" width="52.005" customWidth="1" bestFit="1"/>
   </cols>
@@ -638,7 +635,7 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="3" t="s">
@@ -679,7 +676,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="37.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="27" customFormat="1" s="1">
       <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
@@ -689,18 +686,22 @@
       <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="6"/>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E3" s="6"/>
       <c r="F3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="6"/>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6">
         <f>COUNTIF(C3:H3,"X")</f>
       </c>
       <c r="J3" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>16</v>
@@ -735,7 +736,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="37.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="28.5" customFormat="1" s="1">
       <c r="A5" s="4" t="s">
         <v>19</v>
       </c>
@@ -760,7 +761,7 @@
         <f>COUNTIF(C5:H5,"X")</f>
       </c>
       <c r="J5" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>21</v>
@@ -791,7 +792,7 @@
         <v>23</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="37.5" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="28.5" customFormat="1" s="1">
       <c r="A7" s="4" t="s">
         <v>24</v>
       </c>
@@ -840,14 +841,12 @@
         <v>13</v>
       </c>
       <c r="G8" s="6"/>
-      <c r="H8" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="H8" s="2"/>
       <c r="I8" s="6">
-        <f>COUNTIF(C8:H8,"X")</f>
+        <v>2</v>
       </c>
       <c r="J8" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>29</v>
@@ -907,7 +906,7 @@
         <v>33</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="27" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="28.5" customFormat="1" s="1">
       <c r="A11" s="4" t="s">
         <v>34</v>
       </c>
@@ -921,7 +920,7 @@
         <v>13</v>
       </c>
       <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
+      <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
         <v>13</v>
       </c>
@@ -948,7 +947,9 @@
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
+      <c r="F12" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
       </c>
@@ -1002,7 +1003,9 @@
       <c r="E14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="6"/>
+      <c r="F14" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
       </c>
@@ -1017,12 +1020,12 @@
         <v>45</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="17.25" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="28.5" customFormat="1" s="1">
       <c r="A15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>47</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>13</v>
@@ -1041,15 +1044,15 @@
         <v>1</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="28.5" customFormat="1" s="1">
       <c r="A16" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>50</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -1066,13 +1069,13 @@
         <v>1</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="20.25">
       <c r="A17" s="8"/>
       <c r="B17" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C17" s="3">
         <f>COUNTIF(C2:C16,"X")</f>
